--- a/output/(山本)整合性_構造性_再構成.xlsx
+++ b/output/(山本)整合性_構造性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,33 +461,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>文書の論理構造に基づき、章・節・項の見出しレベルを飛ばさずに順序立てて構成し、上位見出しが下位見出しを包含する階層関係を維持している。</t>
+          <t>上位の見出しと下位の見出しの間に包含関係の矛盾が生じないよう、システムの機能要件および非機能要件の粒度に合わせて見出しを論理的に階層化し、目次から仕様の全体構造が把握できるように記述している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】基本設計書において「2.ログイン機能」の直下に、節レベルを欠落させて「2.0.1DB接続」という項見出しを配置している（見出しレベルの設定が不適切）。
-→【適合例】「2.ログイン機能」の配下に「2.1機能概要」「2.2処理詳細」等の節見出しを順序立てて設け、文書の階層構造を段階的に詳細化している。</t>
+【非適合例】1.ユーザー管理機能
+1.1.ユーザー登録
+2.ユーザー削除（「ユーザー削除」が「ユーザー管理機能」の下位機能であるにもかかわらず、同列の見出しレベルで記述されており、包含関係に矛盾が生じている。）
+→【適合例】1.ユーザー管理機能
+1.1.ユーザー登録
+1.2.ユーザー削除（「ユーザー削除」を「ユーザー管理機能」の下位階層に配置し、機能の包含関係を論理的に構造化している。）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>文書の構成（見出しレベルの付け方など）が適切である</t>
+          <t>図表内の構成が整っている</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>同一階層にある見出し間の抽象度や情報量を揃え、各章における説明順序や構成要素（目的、定義、詳細等）を全編にわたって統一している。</t>
+          <t>データベース定義書やAPIインターフェース仕様書において表形式で仕様を提示する際、パラメータの必須属性や処理の順序といった論理的な関連性に基づく明確な配列基準を設け、その規定に従って項目を配置している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】設計書の第1章では「機能詳細」を記述しているが、第2章では「画面遷移」のみを記述するなど、章によって扱う情報の粒度や項目構成が不揃いである。
-→【適合例】全ての機能章において「目的」「入出力」「処理手順」の項目構成を統一し、読み手が特定の情報を探しやすい構造的な一貫性を確保している。</t>
+【非適合例】［APIパラメータ一覧表］備考（任意）、ユーザーID（必須）、更新日時（任意）、パスワード（必須）の順で列挙している。（項目の配列に規則性がなく、必須項目と任意項目が混在しているため、実装時に必須パラメータを見落とすリスクがある。）
+→【適合例】［APIパラメータ一覧表］ユーザーID（必須）、パスワード（必須）、更新日時（任意）、備考（任意）の順に列挙している。（必須パラメータを上部にまとめ、論理的な重要度に基づいて配列することで、仕様の確認漏れを防止している。）</t>
         </is>
       </c>
     </row>
@@ -499,33 +503,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>フロー図や構成図等の図において、要素間の関係性（実行順序、因果関係、データ流等）に基づき、視線の動きを考慮した配置規則（左から右、上から下等）を一貫して適用している。</t>
+          <t>システム構成図や業務フロー図において、データの流れや処理の依存関係を、情報の入力から出力へと向かう一貫した方向（左から右、または上から下）に整理し、交差や逆行を最小限に抑えて配置している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】業務フロー図において、処理の開始地点が右下に配置され、処理順序を示す矢印が上下左右に複雑に交差している（情報の関連性が理解しにくい）。
-→【適合例】図内の要素を処理の時系列に沿って左上から右下へ向かって論理的に配置し、情報の流れが一目で把握できるレイアウトを採用している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>図表内の構成が整っている</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>表形式のデータにおいて、情報を共通の属性やカテゴリで分類し、適切な見出し行や列を設けて情報の包含関係や対比関係を構造的に表現している。</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】エラーコード定義表において、ネットワーク通信エラーとアプリケーションの業務チェックエラーが分類されず混在して並んでいる（図表の内容が整理されていない）。
-→【適合例】エラーコードを「通信系」「DB系」「業務バリデーション系」等のカテゴリで明示的に分類し、見出し行を設けて各属性を構造化している。</t>
+【非適合例】システム構成図において、クライアントからWebサーバーへの通信を右から左へ、Webサーバーからデータベースサーバーへの通信を左から右へと描画している。（情報の流れが逆行し、かつ通信線が交差しているため、システム全体の連携順序を誤認する要因となる。）
+→【適合例】システム構成図において、クライアント、Webサーバー、データベースサーバーを左から右へ順に配置し、データの流れを単一の方向で描画している。（コンポーネントの配置をデータの流れに沿って一方向へ整理することで、通信の依存関係を直感的に把握可能にしている。）</t>
         </is>
       </c>
     </row>
